--- a/data/trans_orig/IP19C06-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IP19C06-Edad-trans_orig.xlsx
@@ -1802,7 +1802,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>4745</t>
+          <t>4335</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1817,7 +1817,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1837,7 +1837,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>4137</t>
+          <t>4072</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1852,7 +1852,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,21%</t>
         </is>
       </c>
     </row>
@@ -1910,7 +1910,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>168956</t>
+          <t>169366</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -1925,7 +1925,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>97,27%</t>
+          <t>97,5%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>333060</t>
+          <t>333125</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,77%</t>
+          <t>98,79%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -2145,7 +2145,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>3836</t>
+          <t>4001</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2160,7 +2160,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2180,7 +2180,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>5225</t>
+          <t>4522</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2195,7 +2195,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,63%</t>
         </is>
       </c>
     </row>
@@ -2253,7 +2253,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>357895</t>
+          <t>357730</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -2268,7 +2268,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>98,94%</t>
+          <t>98,89%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2288,7 +2288,7 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>707436</t>
+          <t>708139</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
@@ -2303,7 +2303,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>99,27%</t>
+          <t>99,37%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -3028,7 +3028,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2932</t>
+          <t>2876</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3043,7 +3043,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3063,7 +3063,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>3383</t>
+          <t>3821</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3078,7 +3078,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3098,7 +3098,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>4661</t>
+          <t>4522</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3113,7 +3113,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,66%</t>
         </is>
       </c>
     </row>
@@ -3136,7 +3136,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>74756</t>
+          <t>74812</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -3151,7 +3151,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,23%</t>
+          <t>96,3%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -3171,7 +3171,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>88681</t>
+          <t>88243</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -3186,7 +3186,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>96,33%</t>
+          <t>95,85%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -3206,7 +3206,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>165090</t>
+          <t>165229</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -3221,7 +3221,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,25%</t>
+          <t>97,34%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -3371,7 +3371,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>3088</t>
+          <t>3523</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3386,7 +3386,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3441,7 +3441,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>3906</t>
+          <t>3529</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3456,7 +3456,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,37%</t>
         </is>
       </c>
     </row>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>121998</t>
+          <t>121563</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -3494,7 +3494,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,53%</t>
+          <t>97,18%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -3549,7 +3549,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>253266</t>
+          <t>253643</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -3564,7 +3564,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,48%</t>
+          <t>98,63%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -3709,12 +3709,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>431</t>
+          <t>429</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>6061</t>
+          <t>6123</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3729,7 +3729,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>4,14%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3749,7 +3749,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>4928</t>
+          <t>5062</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3764,7 +3764,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,59%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1250</t>
+          <t>1241</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>7386</t>
+          <t>7374</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3822,12 +3822,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>141859</t>
+          <t>141797</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>147489</t>
+          <t>147491</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3837,7 +3837,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,9%</t>
+          <t>95,86%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -3857,7 +3857,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>136255</t>
+          <t>136121</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -3872,7 +3872,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>96,51%</t>
+          <t>96,41%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>281717</t>
+          <t>281729</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>287853</t>
+          <t>287862</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1127</t>
+          <t>1128</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>7336</t>
+          <t>7279</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4072,7 +4072,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>622</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>6120</t>
+          <t>6206</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,01%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2505</t>
+          <t>2520</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>10386</t>
+          <t>10312</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4142,7 +4142,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,43%</t>
         </is>
       </c>
     </row>
@@ -4165,12 +4165,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>346655</t>
+          <t>346712</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>352864</t>
+          <t>352863</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4180,7 +4180,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>97,93%</t>
+          <t>97,94%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -4200,12 +4200,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>359882</t>
+          <t>359796</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>365984</t>
+          <t>365380</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4215,12 +4215,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>98,33%</t>
+          <t>98,3%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,99%</t>
+          <t>99,83%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>709607</t>
+          <t>709681</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>717488</t>
+          <t>717473</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,7 +4250,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>98,56%</t>
+          <t>98,57%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -4975,7 +4975,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4397</t>
+          <t>3945</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4990,7 +4990,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,46%</t>
+          <t>5,8%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5045,7 +5045,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>4652</t>
+          <t>3863</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5060,7 +5060,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>2,57%</t>
         </is>
       </c>
     </row>
@@ -5083,7 +5083,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>63663</t>
+          <t>64115</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -5098,7 +5098,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>93,54%</t>
+          <t>94,2%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -5153,7 +5153,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>145537</t>
+          <t>146326</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -5168,7 +5168,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,9%</t>
+          <t>97,43%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -5661,7 +5661,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3456</t>
+          <t>3197</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5676,7 +5676,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5696,7 +5696,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>3796</t>
+          <t>2843</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5711,7 +5711,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5731,7 +5731,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>4680</t>
+          <t>4101</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5746,7 +5746,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,46%</t>
         </is>
       </c>
     </row>
@@ -5769,7 +5769,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>141649</t>
+          <t>141908</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -5784,7 +5784,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,62%</t>
+          <t>97,8%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -5804,7 +5804,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>131459</t>
+          <t>132412</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -5819,7 +5819,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>97,19%</t>
+          <t>97,9%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -5839,7 +5839,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>275680</t>
+          <t>276259</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -5854,7 +5854,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,33%</t>
+          <t>98,54%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -6004,7 +6004,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>4644</t>
+          <t>4974</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6019,7 +6019,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6039,7 +6039,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>3520</t>
+          <t>3513</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6054,7 +6054,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>619</t>
+          <t>612</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>6144</t>
+          <t>5975</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6089,7 +6089,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,82%</t>
         </is>
       </c>
     </row>
@@ -6112,7 +6112,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>357974</t>
+          <t>357644</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -6127,7 +6127,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>98,72%</t>
+          <t>98,63%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -6147,7 +6147,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>364488</t>
+          <t>364495</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -6162,7 +6162,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>99,04%</t>
+          <t>99,05%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>724482</t>
+          <t>724651</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>730007</t>
+          <t>730014</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,7 +6197,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>99,16%</t>
+          <t>99,18%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -6922,7 +6922,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3376</t>
+          <t>3326</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6937,7 +6937,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,1%</t>
+          <t>5,02%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6957,7 +6957,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>5562</t>
+          <t>4750</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6972,7 +6972,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,21%</t>
+          <t>6,16%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6987,12 +6987,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>389</t>
+          <t>387</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>6290</t>
+          <t>6305</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7007,7 +7007,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>4,4%</t>
         </is>
       </c>
     </row>
@@ -7030,7 +7030,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>62820</t>
+          <t>62870</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -7045,7 +7045,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>94,9%</t>
+          <t>94,98%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -7065,7 +7065,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>71569</t>
+          <t>72381</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -7080,7 +7080,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>92,79%</t>
+          <t>93,84%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -7100,12 +7100,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>137037</t>
+          <t>137022</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>142938</t>
+          <t>142940</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7115,7 +7115,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>95,61%</t>
+          <t>95,6%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -7260,12 +7260,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>675</t>
+          <t>681</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>6123</t>
+          <t>6065</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7275,12 +7275,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>4,98%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7330,12 +7330,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>741</t>
+          <t>671</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>6980</t>
+          <t>6307</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7345,12 +7345,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,2%</t>
         </is>
       </c>
     </row>
@@ -7373,12 +7373,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>115780</t>
+          <t>115838</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>121228</t>
+          <t>121222</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7388,12 +7388,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>94,98%</t>
+          <t>95,02%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,45%</t>
+          <t>99,44%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7443,12 +7443,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>279711</t>
+          <t>280384</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>285950</t>
+          <t>286020</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7458,12 +7458,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,57%</t>
+          <t>97,8%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,74%</t>
+          <t>99,77%</t>
         </is>
       </c>
     </row>
@@ -7603,12 +7603,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>712</t>
+          <t>698</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>6158</t>
+          <t>5893</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7618,12 +7618,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7643,7 +7643,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>7496</t>
+          <t>6631</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7658,7 +7658,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7673,12 +7673,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>782</t>
+          <t>776</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>9142</t>
+          <t>8957</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7693,7 +7693,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,06%</t>
         </is>
       </c>
     </row>
@@ -7716,12 +7716,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>191579</t>
+          <t>191844</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>197025</t>
+          <t>197039</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7731,12 +7731,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,89%</t>
+          <t>97,02%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,64%</t>
+          <t>99,65%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7751,7 +7751,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>229712</t>
+          <t>230577</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -7766,7 +7766,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>96,84%</t>
+          <t>97,2%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -7786,12 +7786,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>425803</t>
+          <t>425988</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>434163</t>
+          <t>434169</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7801,7 +7801,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,9%</t>
+          <t>97,94%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -7946,12 +7946,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2657</t>
+          <t>2765</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>10494</t>
+          <t>11093</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7961,12 +7961,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7986,7 +7986,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>8558</t>
+          <t>8563</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8016,12 +8016,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>4279</t>
+          <t>4082</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>15396</t>
+          <t>15143</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8031,12 +8031,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,73%</t>
         </is>
       </c>
     </row>
@@ -8059,12 +8059,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>381139</t>
+          <t>380540</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>388976</t>
+          <t>388868</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8074,12 +8074,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>97,32%</t>
+          <t>97,17%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,32%</t>
+          <t>99,29%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8094,7 +8094,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>475886</t>
+          <t>475881</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -8129,12 +8129,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>860680</t>
+          <t>860933</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>871797</t>
+          <t>871994</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8144,12 +8144,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>98,24%</t>
+          <t>98,27%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,51%</t>
+          <t>99,53%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP19C06-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IP19C06-Edad-trans_orig.xlsx
@@ -544,7 +544,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -555,7 +555,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -836,47 +836,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>1893</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>3906</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>1893</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -949,57 +949,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>1893</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>1893</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>1893</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>3906</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>3906</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>3906</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>1893</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>1893</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>1893</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1179,47 +1179,47 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>123</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>80418</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>127</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>84335</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>123</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>80418</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
@@ -1292,57 +1292,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>123</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>80418</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>80418</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>80418</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>127</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>84335</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>84335</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>84335</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>123</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>80418</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>80418</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>80418</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1522,47 +1522,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>158</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>105719</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>148</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>99193</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>158</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>105719</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
@@ -1635,57 +1635,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>158</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>105719</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>105719</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>105719</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>148</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>99193</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>99193</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>99193</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>158</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>105719</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>105719</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>105719</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1752,107 +1752,107 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>1219</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>4529</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>0,7%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>2,61%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K13" s="2" t="inlineStr">
+      <c r="R13" s="2" t="inlineStr">
         <is>
           <t>1219</t>
         </is>
       </c>
-      <c r="L13" s="2" t="inlineStr">
+      <c r="S13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>4335</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>0,7%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>4546</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>0,36%</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>2,5%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>1219</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>4072</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>0,36%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,35%</t>
         </is>
       </c>
     </row>
@@ -1865,72 +1865,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>259</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>172482</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>169172</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>173701</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>99,3%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>97,39%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>241</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>163497</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>259</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>172482</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>169366</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>173701</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>99,3%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>97,5%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>333125</t>
+          <t>332651</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,79%</t>
+          <t>98,65%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -1978,57 +1978,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>261</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>173701</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>173701</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>173701</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>241</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>163497</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>163497</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>163497</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>261</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>173701</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>173701</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>173701</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2095,107 +2095,107 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>1219</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>4350</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>0,34%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>1,2%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K16" s="2" t="inlineStr">
+      <c r="R16" s="2" t="inlineStr">
         <is>
           <t>1219</t>
         </is>
       </c>
-      <c r="L16" s="2" t="inlineStr">
+      <c r="S16" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>4001</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>0,34%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>4387</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>0,17%</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>1,11%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>1219</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>4522</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>0,17%</t>
-        </is>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,62%</t>
         </is>
       </c>
     </row>
@@ -2208,72 +2208,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>543</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>360512</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>357381</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>361731</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>99,66%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>98,8%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>522</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>350930</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>543</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>360512</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>357730</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>361731</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>99,66%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>98,89%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,7 +2288,7 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>708139</t>
+          <t>708274</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
@@ -2303,7 +2303,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>99,37%</t>
+          <t>99,38%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -2321,57 +2321,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>545</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>361731</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>361731</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>361731</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>522</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>350930</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>350930</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>350930</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>545</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>361731</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>361731</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>361731</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2491,7 +2491,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -2502,7 +2502,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -2783,47 +2783,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>669</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>3298</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>669</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -2896,57 +2896,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>669</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>669</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>669</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>3298</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>3298</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>3298</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>669</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>669</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>669</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3018,102 +3018,102 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
+          <t>742</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>3784</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>0,81%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>4,11%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
           <t>582</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>2876</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>3419</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>0,75%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>3,7%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>742</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>4,4%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>1324</t>
+        </is>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>3821</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>0,81%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>4655</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>0,78%</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>4,15%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>1324</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>4522</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>0,78%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,74%</t>
         </is>
       </c>
     </row>
@@ -3126,74 +3126,74 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>123</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>91322</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>88280</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>92064</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>99,19%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>95,89%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>109</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>77106</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>74812</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>74269</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
         <is>
           <t>77688</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>99,25%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>96,3%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>95,6%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>123</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>91322</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>88243</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>92064</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>99,19%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>95,85%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
           <t>232</t>
@@ -3206,7 +3206,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>165229</t>
+          <t>165096</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -3221,7 +3221,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,34%</t>
+          <t>97,26%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -3239,57 +3239,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>124</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>92064</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>92064</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>92064</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>110</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>77688</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>77688</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>77688</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>124</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>92064</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>92064</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>92064</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3356,107 +3356,107 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>698</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>3523</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>3205</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>0,56%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="O10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>2,82%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>2,56%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>698</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>3499</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>0,27%</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>698</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>3529</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>0,27%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,36%</t>
         </is>
       </c>
     </row>
@@ -3469,74 +3469,74 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>190</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>132086</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>177</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>124388</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>121563</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>121881</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
         <is>
           <t>125086</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>99,44%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>97,18%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>97,44%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>190</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>132086</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
           <t>367</t>
@@ -3549,7 +3549,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>253643</t>
+          <t>253673</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -3564,7 +3564,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,63%</t>
+          <t>98,64%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -3582,57 +3582,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>190</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>132086</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>132086</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>132086</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>178</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>125086</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>125086</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>125086</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>190</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>132086</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>132086</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>132086</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3699,72 +3699,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>1481</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>5387</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>1,05%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>3,82%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>1950</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>429</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>6123</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>430</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>5700</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>1,32%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>0,29%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>4,14%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>1481</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>5062</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>1,05%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1241</t>
+          <t>1258</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>7374</t>
+          <t>7468</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,58%</t>
         </is>
       </c>
     </row>
@@ -3812,74 +3812,74 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>207</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>139702</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>135796</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>141183</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>98,95%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>96,18%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>208</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>145970</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>141797</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>147491</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>142220</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>147490</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>98,68%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>95,86%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>96,15%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
         <is>
           <t>99,71%</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>207</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>139702</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>136121</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>141183</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>98,95%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>96,41%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
           <t>415</t>
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>281729</t>
+          <t>281635</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>287862</t>
+          <t>287845</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,45%</t>
+          <t>97,42%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,57%</t>
+          <t>99,56%</t>
         </is>
       </c>
     </row>
@@ -3925,57 +3925,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>209</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>141183</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>141183</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>141183</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>211</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>147920</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>147920</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>147920</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>209</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>141183</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>141183</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>141183</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4042,72 +4042,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>2223</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>616</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>6517</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>0,61%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>0,17%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>1,78%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>3230</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>1128</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>7279</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>1142</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>7087</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>0,91%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="O16" s="2" t="inlineStr">
         <is>
           <t>0,32%</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>2,06%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>2223</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>622</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>6206</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>0,61%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>0,17%</t>
-        </is>
-      </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2520</t>
+          <t>2413</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>10312</t>
+          <t>9915</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,38%</t>
         </is>
       </c>
     </row>
@@ -4155,74 +4155,74 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>521</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>363779</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>359485</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>365386</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>99,39%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>98,22%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>99,83%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>499</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>350761</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>346712</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>352863</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>346904</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>352849</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>99,09%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>97,94%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>98,0%</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
         <is>
           <t>99,68%</t>
         </is>
       </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>521</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>363779</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>359796</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>365380</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>99,39%</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>98,3%</t>
-        </is>
-      </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>99,83%</t>
-        </is>
-      </c>
       <c r="Q17" s="2" t="inlineStr">
         <is>
           <t>1020</t>
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>709681</t>
+          <t>710078</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>717473</t>
+          <t>717580</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>98,57%</t>
+          <t>98,62%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,65%</t>
+          <t>99,66%</t>
         </is>
       </c>
     </row>
@@ -4268,57 +4268,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>524</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>366002</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>366002</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>366002</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>504</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>353991</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>353991</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>353991</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>524</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>366002</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>366002</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>366002</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4438,7 +4438,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -4449,7 +4449,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -4730,47 +4730,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>1284</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>536</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>1284</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -4843,57 +4843,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>1284</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>1284</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>1284</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>536</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>536</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>536</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>1284</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>1284</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>1284</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4960,92 +4960,92 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>771</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>3945</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>3827</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>1,13%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>5,8%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>5,62%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>771</t>
+        </is>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>771</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>3863</t>
+          <t>3866</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5073,74 +5073,74 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>118</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>82129</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>103</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>67289</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>64115</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>64233</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
         <is>
           <t>68060</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>98,87%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>94,2%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>94,38%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>118</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>82129</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
           <t>221</t>
@@ -5153,7 +5153,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>146326</t>
+          <t>146323</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -5186,57 +5186,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>118</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>82129</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>82129</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>82129</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>104</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>68060</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>68060</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>68060</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>118</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>82129</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>82129</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>82129</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5416,47 +5416,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>207</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>149341</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>214</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>148917</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>207</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>149341</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
@@ -5529,57 +5529,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>207</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>149341</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>149341</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>149341</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>214</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>148917</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>148917</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>148917</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>207</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>149341</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>149341</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>149341</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5651,102 +5651,102 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
+          <t>700</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>3557</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>0,52%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>2,63%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
           <t>617</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>3197</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>3170</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>0,43%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>2,2%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>700</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>2,18%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>1317</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>2843</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>0,52%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>4627</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>0,47%</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>2,1%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>1317</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>4101</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>0,47%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,65%</t>
         </is>
       </c>
     </row>
@@ -5759,74 +5759,74 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>182</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>134555</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>131698</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>135255</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>99,48%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>97,37%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>207</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>144488</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>141908</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>141935</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
         <is>
           <t>145105</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>99,57%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>97,8%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>97,82%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>182</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>134555</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>132412</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>135255</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>99,48%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>97,9%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
           <t>389</t>
@@ -5839,7 +5839,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>276259</t>
+          <t>275733</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -5854,7 +5854,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,54%</t>
+          <t>98,35%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -5872,57 +5872,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>183</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>135255</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>135255</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>135255</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>208</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>145105</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>145105</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>145105</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>183</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>135255</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>135255</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>135255</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5989,107 +5989,107 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>700</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>3503</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>0,19%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>0,95%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>1388</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>4974</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>5418</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>0,38%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="O16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>1,37%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>700</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>1,49%</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
+          <t>2088</t>
+        </is>
+      </c>
+      <c r="S16" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>3513</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>0,19%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>5556</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>0,29%</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>0,95%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>2088</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>612</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>5975</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>0,29%</t>
-        </is>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>0,08%</t>
-        </is>
-      </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,76%</t>
         </is>
       </c>
     </row>
@@ -6102,107 +6102,107 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>509</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>367308</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>364505</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>368008</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>99,81%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>99,05%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>525</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>361230</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>357644</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>357200</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
         <is>
           <t>362618</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>99,62%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>98,63%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>98,51%</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>509</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>367308</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>364495</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>368008</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>99,81%</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>99,05%</t>
-        </is>
-      </c>
-      <c r="P17" s="2" t="inlineStr">
+      <c r="Q17" s="2" t="inlineStr">
+        <is>
+          <t>1034</t>
+        </is>
+      </c>
+      <c r="R17" s="2" t="inlineStr">
+        <is>
+          <t>728538</t>
+        </is>
+      </c>
+      <c r="S17" s="2" t="inlineStr">
+        <is>
+          <t>725070</t>
+        </is>
+      </c>
+      <c r="T17" s="2" t="inlineStr">
+        <is>
+          <t>730626</t>
+        </is>
+      </c>
+      <c r="U17" s="2" t="inlineStr">
+        <is>
+          <t>99,71%</t>
+        </is>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
+          <t>99,24%</t>
+        </is>
+      </c>
+      <c r="W17" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
-        </is>
-      </c>
-      <c r="Q17" s="2" t="inlineStr">
-        <is>
-          <t>1034</t>
-        </is>
-      </c>
-      <c r="R17" s="2" t="inlineStr">
-        <is>
-          <t>728538</t>
-        </is>
-      </c>
-      <c r="S17" s="2" t="inlineStr">
-        <is>
-          <t>724651</t>
-        </is>
-      </c>
-      <c r="T17" s="2" t="inlineStr">
-        <is>
-          <t>730014</t>
-        </is>
-      </c>
-      <c r="U17" s="2" t="inlineStr">
-        <is>
-          <t>99,71%</t>
-        </is>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>99,18%</t>
-        </is>
-      </c>
-      <c r="W17" s="2" t="inlineStr">
-        <is>
-          <t>99,92%</t>
         </is>
       </c>
     </row>
@@ -6215,57 +6215,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>510</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>368008</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>368008</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>368008</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>527</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>362618</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>362618</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>362618</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>510</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>368008</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>368008</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>368008</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6385,7 +6385,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -6396,7 +6396,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -6677,64 +6677,64 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>4676</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>5797</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>6072</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>5316</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
           <t>—%</t>
@@ -6752,7 +6752,7 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>11113</t>
+          <t>10748</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
@@ -6790,57 +6790,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>4676</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>4676</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>4676</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>5797</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>5797</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>5797</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>5316</t>
+          <t>6072</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>5316</t>
+          <t>6072</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>5316</t>
+          <t>6072</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6865,17 +6865,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>11113</t>
+          <t>10748</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>11113</t>
+          <t>10748</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>11113</t>
+          <t>10748</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6907,72 +6907,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>964</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>5164</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>1,43%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>7,64%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>931</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>819</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>3326</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>1,41%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>2723</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>1,29%</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>5,02%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>1045</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>4750</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>1,35%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>6,16%</t>
+          <t>4,29%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6982,22 +6982,22 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>1976</t>
+          <t>1783</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>387</t>
+          <t>349</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>6305</t>
+          <t>6559</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
@@ -7007,7 +7007,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>5,01%</t>
         </is>
       </c>
     </row>
@@ -7020,74 +7020,74 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>107</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>66606</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>62406</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>67570</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>98,57%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>92,36%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>101</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>65265</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>62870</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>66196</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>98,59%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>94,98%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>62630</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>60726</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>63449</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>98,71%</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>95,71%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>107</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>76086</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>72381</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>77131</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>98,65%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>93,84%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
           <t>208</t>
@@ -7095,27 +7095,27 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>141351</t>
+          <t>129237</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>137022</t>
+          <t>124461</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>142940</t>
+          <t>130671</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>98,62%</t>
+          <t>98,64%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>95,6%</t>
+          <t>94,99%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -7133,57 +7133,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>108</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>67570</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>67570</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>67570</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>103</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>66196</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>66196</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>66196</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>108</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>77131</t>
+          <t>63449</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>77131</t>
+          <t>63449</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>77131</t>
+          <t>63449</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7208,17 +7208,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>143327</t>
+          <t>131020</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>143327</t>
+          <t>131020</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>143327</t>
+          <t>131020</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -7250,72 +7250,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>2568</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>681</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>6065</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>2,11%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>0,56%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>4,98%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2507</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>666</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>6151</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>5,05%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7325,17 +7325,17 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>2568</t>
+          <t>2507</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>671</t>
+          <t>743</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>6307</t>
+          <t>6246</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7345,12 +7345,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,25%</t>
         </is>
       </c>
     </row>
@@ -7363,72 +7363,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>186</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>155298</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>159</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>119335</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>115838</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>121222</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>97,89%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>95,02%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>99,44%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>186</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>164788</t>
+          <t>119333</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>115689</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>121174</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>97,94%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>94,95%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>99,45%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7438,17 +7438,17 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>284123</t>
+          <t>274631</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>280384</t>
+          <t>270892</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>286020</t>
+          <t>276395</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7458,12 +7458,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,8%</t>
+          <t>97,75%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,77%</t>
+          <t>99,73%</t>
         </is>
       </c>
     </row>
@@ -7476,57 +7476,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>186</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>155298</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>155298</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>155298</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>163</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>121903</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>121903</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>121903</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>186</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>164788</t>
+          <t>121840</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>164788</t>
+          <t>121840</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>164788</t>
+          <t>121840</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7551,17 +7551,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>286691</t>
+          <t>277138</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>286691</t>
+          <t>277138</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>286691</t>
+          <t>277138</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7593,72 +7593,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>641</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>3738</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>0,27%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>1,6%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>2259</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>698</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>5893</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>1,14%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>0,35%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>2,98%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>1332</t>
+          <t>2363</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>754</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>6631</t>
+          <t>6224</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7668,22 +7668,22 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>3591</t>
+          <t>3003</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>776</t>
+          <t>783</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>8957</t>
+          <t>7478</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
@@ -7693,7 +7693,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>1,71%</t>
         </is>
       </c>
     </row>
@@ -7706,72 +7706,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>267</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>232909</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>229812</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>233550</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>99,73%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>98,4%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>274</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>195478</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>191844</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>197039</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>98,86%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>97,02%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>99,65%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>267</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>235876</t>
+          <t>202553</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>230577</t>
+          <t>198692</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>237208</t>
+          <t>204162</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>99,44%</t>
+          <t>98,85%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>97,2%</t>
+          <t>96,96%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>99,63%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7781,27 +7781,27 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>431354</t>
+          <t>435463</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>425988</t>
+          <t>430988</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>434169</t>
+          <t>437683</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>99,17%</t>
+          <t>99,32%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,94%</t>
+          <t>98,29%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -7819,57 +7819,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>268</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>233550</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>233550</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>233550</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>277</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>197737</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>197737</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>197737</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>268</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>237208</t>
+          <t>204916</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>237208</t>
+          <t>204916</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>237208</t>
+          <t>204916</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7894,17 +7894,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>434945</t>
+          <t>438466</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>434945</t>
+          <t>438466</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>434945</t>
+          <t>438466</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -7936,72 +7936,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>1605</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>5834</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>0,35%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>1,27%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>5758</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>2765</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>11093</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>1,47%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>0,71%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>2,83%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>2377</t>
+          <t>5689</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2789</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>8563</t>
+          <t>10451</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8011,32 +8011,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>8135</t>
+          <t>7294</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>4082</t>
+          <t>3587</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>15143</t>
+          <t>12528</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,46%</t>
         </is>
       </c>
     </row>
@@ -8049,72 +8049,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>568</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>459490</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>455261</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>461095</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>99,65%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>98,73%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>545</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>385875</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>380540</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>388868</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>98,53%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>97,17%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>99,29%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>568</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>482067</t>
+          <t>390589</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>475881</t>
+          <t>385827</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>484444</t>
+          <t>393489</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>99,51%</t>
+          <t>98,56%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>98,23%</t>
+          <t>97,36%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>99,3%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8124,32 +8124,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>867941</t>
+          <t>850078</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>860933</t>
+          <t>844844</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>871994</t>
+          <t>853785</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>99,07%</t>
+          <t>99,15%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>98,27%</t>
+          <t>98,54%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,53%</t>
+          <t>99,58%</t>
         </is>
       </c>
     </row>
@@ -8162,57 +8162,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>570</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>461095</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>461095</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>461095</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>554</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>391633</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>391633</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>391633</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>570</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>484444</t>
+          <t>396278</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>484444</t>
+          <t>396278</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>484444</t>
+          <t>396278</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8237,17 +8237,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>876076</t>
+          <t>857372</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>876076</t>
+          <t>857372</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>876076</t>
+          <t>857372</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
